--- a/banks/W07_Kahoot匯入.xlsx
+++ b/banks/W07_Kahoot匯入.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -491,30 +491,30 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>共價修飾</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>酵素動力學</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>不可逆抑制</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>回饋抑制</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>不可逆抑制</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>酵素動力學</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>共價修飾</t>
-        </is>
-      </c>
       <c r="F2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -531,12 +531,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>回饋抑制</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
           <t>酵素動力學</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>回饋抑制</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -561,30 +561,30 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>米氏常數</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>雙倒數作圖</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>米氏常數</t>
-        </is>
-      </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>共價修飾</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>米氏方程式</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>共價修飾</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -596,19 +596,19 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>米氏方程式</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>最大速率</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>酵素動力學</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>米氏方程式</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>轉換數</t>
@@ -619,7 +619,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -631,30 +631,30 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>米氏常數</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>初速率</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>米氏常數</t>
-        </is>
-      </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>抑制劑</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>轉換數</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>抑制劑</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -666,30 +666,30 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>初速率</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>米氏常數</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>磷酸化</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>轉換數</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>初速率</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>磷酸化</t>
-        </is>
-      </c>
       <c r="F7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -701,30 +701,30 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>抑制劑</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
           <t>回饋抑制</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>磷酸化</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>初速率</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>抑制劑</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -776,14 +776,14 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>最大速率</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>非競爭性抑制</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>最大速率</t>
-        </is>
-      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>不可逆抑制</t>
@@ -794,7 +794,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -806,30 +806,30 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>回饋抑制</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>雙倒數作圖</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>競爭性抑制</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>不可逆抑制</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>回饋抑制</t>
-        </is>
-      </c>
       <c r="F11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -841,30 +841,30 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>共價修飾</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>雙倒數作圖</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>酵素動力學</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>回饋抑制</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>共價修飾</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>酵素動力學</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>雙倒數作圖</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -876,17 +876,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
+          <t>酵素動力學</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>轉換數</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>最大速率</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>轉換數</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>酵素動力學</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -911,30 +911,30 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>回饋抑制</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>最大速率</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>共價修飾</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>磷酸化</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>共價修飾</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>回饋抑制</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>最大速率</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -946,30 +946,170 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>轉換數</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>米氏常數</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>磷酸化</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>最大速率</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>米氏常數</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>轉換數</t>
-        </is>
-      </c>
       <c r="F15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>(標圖:抑制作用比較圖) 標號1所在的紅色曲線代表哪一種抑制作用?</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>回饋抑制</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>競爭性抑制</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>不可逆抑制</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>非競爭性抑制</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>(標圖:抑制作用比較圖) 標號2所在的紅色曲線代表哪一種抑制作用?</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>非競爭性抑制</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>競爭性抑制</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>共價修飾</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>回饋抑制</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>哪一個配對正確?</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>競爭性抑制—抑制劑搶佔活性部位</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>回饋抑制—第一個酵素抑制最終產物</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>非競爭性抑制—加大量受質就能解除</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>磷酸化—永久破壞酵素結構</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>已知某酵素Vmax為80 μmol/min。當[S]=Km時v0大約是多少?</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>160 μmol/min</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>80 μmol/min</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>20 μmol/min</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>40 μmol/min</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
